--- a/Тест2/275.xlsx
+++ b/Тест2/275.xlsx
@@ -210,16 +210,16 @@
     <t xml:space="preserve">Gomogenlash natijasida nima yuz beradi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Mikroblar nobud bo'ladi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mikroblar sporaga aylanadi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mikroblar ko'payib ketadi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mikroblar bir joyda to'planadi</t>
+    <t xml:space="preserve">Mikroblar butunlay nobud bo'lib ketadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mikroblar sporaga aylanib qoladi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mikroblar ko'payib, soni oshib ketadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mikroblar bir joyda to'planib qoladi</t>
   </si>
   <si>
     <t xml:space="preserve">Mikroblar suyuqlikda tekis taqsimlanadi</t>
